--- a/data/processed/Revenue Exposure.xlsx
+++ b/data/processed/Revenue Exposure.xlsx
@@ -62030,8 +62030,8 @@
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Documento" ma:contentTypeID="0x010100086DC0FFDEFA864DA147FFDEA823F2EE" ma:contentTypeVersion="3" ma:contentTypeDescription="Creare un nuovo documento." ma:contentTypeScope="" ma:versionID="efa000e167d9ce5db8cd2eb5b6f87cd4">
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="c41a64fd-65ba-4a6e-8004-8ade4c8fdb39" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="1f94584ddf2c7798ba84aeef6e679263" ns2:_="">
+<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100086DC0FFDEFA864DA147FFDEA823F2EE" ma:contentTypeVersion="3" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="39870545afabb502c4050089500bd5b6">
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="c41a64fd-65ba-4a6e-8004-8ade4c8fdb39" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="9bb2a11c505461e40f497f8b9cdcbcf5" ns2:_="">
     <xsd:import namespace="c41a64fd-65ba-4a6e-8004-8ade4c8fdb39"/>
     <xsd:element name="properties">
       <xsd:complexType>
@@ -62077,8 +62077,8 @@
         <xsd:element ref="dc:creator" minOccurs="0" maxOccurs="1"/>
         <xsd:element ref="dcterms:created" minOccurs="0" maxOccurs="1"/>
         <xsd:element ref="dc:identifier" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="contentType" minOccurs="0" maxOccurs="1" type="xsd:string" ma:index="0" ma:displayName="Tipo di contenuto"/>
-        <xsd:element ref="dc:title" minOccurs="0" maxOccurs="1" ma:index="4" ma:displayName="Titolo"/>
+        <xsd:element name="contentType" minOccurs="0" maxOccurs="1" type="xsd:string" ma:index="0" ma:displayName="Content Type"/>
+        <xsd:element ref="dc:title" minOccurs="0" maxOccurs="1" ma:index="4" ma:displayName="Title"/>
         <xsd:element ref="dc:subject" minOccurs="0" maxOccurs="1"/>
         <xsd:element ref="dc:description" minOccurs="0" maxOccurs="1"/>
         <xsd:element name="keywords" minOccurs="0" maxOccurs="1" type="xsd:string"/>
@@ -62192,19 +62192,5 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{7136A550-8F51-42BC-9C7D-4B99158D3FFC}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="c41a64fd-65ba-4a6e-8004-8ade4c8fdb39"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{89DDE55F-16AF-462E-A9F0-01F805372CC1}"/>
 </file>